--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sdsuedu-my.sharepoint.com/personal/lrao1160_sdsu_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lexah\OneDrive\Documents\GitHub\Ophelias-Oasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74684859-9307-4BB8-8D19-F2C038F49AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
@@ -36,6 +36,29 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t xml:space="preserve">Time:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:  </t>
+  </si>
+  <si>
+    <t>Location:  What did the person do?</t>
+  </si>
+  <si>
+    <t>What did the person do:</t>
+  </si>
+  <si>
+    <t>Event 1</t>
+  </si>
+  <si>
+    <t>Event 2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +428,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lexah\OneDrive\Documents\GitHub\Ophelias-Oasis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4872d23a9318b819/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7BAC988-1A59-47D7-9765-A820C93B0542}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="10860" yWindow="1920" windowWidth="22180" windowHeight="14140" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+  <si>
+    <t>Event:</t>
+  </si>
   <si>
     <t xml:space="preserve">Time:  </t>
   </si>
@@ -47,23 +50,77 @@
     <t xml:space="preserve">Date:  </t>
   </si>
   <si>
-    <t>Location:  What did the person do?</t>
-  </si>
-  <si>
-    <t>What did the person do:</t>
-  </si>
-  <si>
-    <t>Event 1</t>
-  </si>
-  <si>
-    <t>Event 2</t>
+    <t>Location:</t>
+  </si>
+  <si>
+    <t>What the person did:</t>
+  </si>
+  <si>
+    <t>6:35PM</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>Fabian formed the group known as "EMU Lation Softwares".  Fabian gathered all of the group members contact information to communicate with each other in a group chat.</t>
+  </si>
+  <si>
+    <t>6:45PM</t>
+  </si>
+  <si>
+    <t>Fabian assigned the project roles of all group members. The project selected is "Ophelias Oasis".</t>
+  </si>
+  <si>
+    <t>10:55AM</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Lexa created a Github repository for the group to program and test the project remotely.</t>
+  </si>
+  <si>
+    <t>5:52PM</t>
+  </si>
+  <si>
+    <t>Cristian created the project notebook which serves as the layout for the project.</t>
+  </si>
+  <si>
+    <t>5:50PM</t>
+  </si>
+  <si>
+    <t>Cristian created the requirements database for listing the function and non-function requirements of the project.</t>
+  </si>
+  <si>
+    <t>6:30PM</t>
+  </si>
+  <si>
+    <t>Lexa created the testing script records that keeps track of all transactions from testing.</t>
+  </si>
+  <si>
+    <t>6:15AM</t>
+  </si>
+  <si>
+    <t>Lexa linked everyone for tracking bugs in the project. Lexa was able to make sure that eveyone was able to get into the github page so that everyone could connect to the server. Lexa was able to reach out the team mates when they were not able to contact the main server. Lexa was able to manage the feature and task on the project to make sure the project worked as intended.</t>
+  </si>
+  <si>
+    <t>8:55AM</t>
+  </si>
+  <si>
+    <t>Lexa created the time tracker sheet to document all group activity in chronological order.</t>
+  </si>
+  <si>
+    <t>7:42PM</t>
+  </si>
+  <si>
+    <t>Evan created the draft document for the UML diagram that will utilized for the first turn-in checkpoint on the 24th.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,8 +149,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,31 +488,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="175.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46268</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46269</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46277</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46280</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46280</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46281</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46281</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46281</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4872d23a9318b819/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7BAC988-1A59-47D7-9765-A820C93B0542}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D82D35A-F0A4-E648-BA7B-541F3399A92B}"/>
   <bookViews>
-    <workbookView xWindow="10860" yWindow="1920" windowWidth="22180" windowHeight="14140" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="14860" windowHeight="21820" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Event:</t>
   </si>
   <si>
-    <t xml:space="preserve">Time:  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Date:  </t>
   </si>
   <si>
@@ -83,15 +80,9 @@
     <t>5:52PM</t>
   </si>
   <si>
-    <t>Cristian created the project notebook which serves as the layout for the project.</t>
-  </si>
-  <si>
     <t>5:50PM</t>
   </si>
   <si>
-    <t>Cristian created the requirements database for listing the function and non-function requirements of the project.</t>
-  </si>
-  <si>
     <t>6:30PM</t>
   </si>
   <si>
@@ -113,14 +104,80 @@
     <t>7:42PM</t>
   </si>
   <si>
-    <t>Evan created the draft document for the UML diagram that will utilized for the first turn-in checkpoint on the 24th.</t>
+    <t>Sean created a proposal text file going over Lexa's comments for testing.  Lexa preposed using an excel document to track the program requirements and then analysis the program using the requirement document.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lexa, create a text file for tracking the project's data on project failures and functions.  Then integrate as much of that code as possible into the project.  This project is stored in Visual Studio.  </t>
+  </si>
+  <si>
+    <t>8:36 AM - 11:56 AM</t>
+  </si>
+  <si>
+    <t>Lexa, finalized the testing script plans and linked it to the Excel document.  Now the program test should be able to sync with the Excel document on macOS and test our program.  This will decrease the total development time.</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Cristian, worked on project book.</t>
+  </si>
+  <si>
+    <t>Minutes Worked</t>
+  </si>
+  <si>
+    <t>Cristian, worked on creating requirements.</t>
+  </si>
+  <si>
+    <t>Cristian, created the requirements database for listing the functional and non-functional requirements of the project.</t>
+  </si>
+  <si>
+    <t>Cristian, created the project notebook which serves as the layout for the project.</t>
+  </si>
+  <si>
+    <t>Sean made a rough estimate of the unadjusted FP computation based on the requirements database.</t>
+  </si>
+  <si>
+    <t>Evan created the UML use case diagram and completed part 6b on the Notebook Template (Discussion of requirements analysis)</t>
+  </si>
+  <si>
+    <t>Evan created the draft document for the UML diagram that will utilized for the first turn-in checkpoint on the 24th. Edit: Changed websites to one more familiar to teammates</t>
+  </si>
+  <si>
+    <t>9:20AM - 10:35AM</t>
+  </si>
+  <si>
+    <t>Cristian, Worked on finishing up the project notebook</t>
+  </si>
+  <si>
+    <t>6:47PM</t>
+  </si>
+  <si>
+    <t>Fabian finalized the Project Notebook and the Timetracker Sheet and submitted them for the project's 1st deliverable.</t>
+  </si>
+  <si>
+    <t>2:00 PM - 4:00PM</t>
+  </si>
+  <si>
+    <t>8:30PM - 12:00AM</t>
+  </si>
+  <si>
+    <t>9:00AM - 12:20PM</t>
+  </si>
+  <si>
+    <t>2:00PM</t>
+  </si>
+  <si>
+    <t>1:30PM</t>
+  </si>
+  <si>
+    <t>During this time period I have intergrated some of the function into the system we are programming.  This was done on Excel document.  I have included the function names.  I have also included some of their discription and the number of function as a demo of the page.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,11 +206,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,6 +227,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,182 +550,453 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="175.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="175.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
-        <v>46266</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46268</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2">
-        <v>46268</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2">
         <v>46269</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2">
         <v>46277</v>
       </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4">
         <v>15</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>46280</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
       <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2">
         <v>46280</v>
       </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="2">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="2">
         <v>46281</v>
       </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
       <c r="E8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2">
         <v>46281</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
       <c r="E9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46281</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="2">
+        <v>46284</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2">
+        <v>46287</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C13" s="4"/>
+      <c r="D13" s="2">
+        <v>46285</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="4">
+        <v>210</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4">
+        <v>120</v>
+      </c>
+      <c r="D15" s="2">
         <v>46281</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4">
+        <v>44</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4">
+        <v>75</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="4">
+        <v>200</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="4">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="4">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46289</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C21" s="4">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46288</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C34" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4872d23a9318b819/Documents/GitHub/Ophelias-Oasis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{EC56A3AD-95B6-44D5-B859-CBB9534D8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D82D35A-F0A4-E648-BA7B-541F3399A92B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D851B0-E2A5-A345-AA39-0818CCACC973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="14860" windowHeight="21820" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>Event:</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>During this time period I have intergrated some of the function into the system we are programming.  This was done on Excel document.  I have included the function names.  I have also included some of their discription and the number of function as a demo of the page.</t>
+  </si>
+  <si>
+    <t>During this time period I added further documentation to the program function.  This allow for me to showcase how the program function work.  This would allow for me to document if the program is working as intended.</t>
+  </si>
+  <si>
+    <t>During this time period in class we worked on the project and incoperated a bunch of the core resources for the program.  This made sure the project had been intergrated as intended.  It also make sure all the components in the project were working as intended.  This would allow for me to do the project like I was required to.  However, it also made sure the cores services in the project were integrated as intended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During this time I added some of the testing script information back.  This made sure the program worked as intended.  The program would work properly if I did that. However, it did not appear to be full done which was the source of my worry.  </t>
   </si>
 </sst>
 </file>
@@ -206,12 +215,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -227,10 +237,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,15 +557,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="175.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="175.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -599,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -619,7 +625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -637,7 +643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -657,7 +663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -677,7 +683,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -692,7 +698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -710,7 +716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -728,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -748,7 +754,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -766,7 +772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -784,7 +790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -802,7 +808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -822,7 +828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -842,7 +848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -859,7 +865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -879,7 +885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -899,7 +905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -919,7 +925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -939,7 +945,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -959,43 +965,94 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C22" s="4">
+        <v>60</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46318</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C23" s="4">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46287</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="4">
+        <v>120</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46320</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C34" s="4"/>
     </row>
   </sheetData>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D851B0-E2A5-A345-AA39-0818CCACC973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD4F264-2070-AA41-A36A-F793F358C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Event:</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t xml:space="preserve">During this time I added some of the testing script information back.  This made sure the program worked as intended.  The program would work properly if I did that. However, it did not appear to be full done which was the source of my worry.  </t>
+  </si>
+  <si>
+    <t>3:40 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1032,24 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C25" s="4"/>
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="4">
+        <v>80</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46322</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C26" s="4"/>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -560,6 +560,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
   <dimension ref="A1:F34"/>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD4F264-2070-AA41-A36A-F793F358C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76B81E0-1B5E-7043-8707-8ADB07BF2546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="4660" yWindow="880" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
   <si>
     <t>Event:</t>
   </si>
@@ -186,6 +186,12 @@
   </si>
   <si>
     <t xml:space="preserve">During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
+  </si>
+  <si>
+    <t>9:00 PM - 12:12 PM</t>
+  </si>
+  <si>
+    <t>During this I finished the rest of the entries in the testing script.  This made sure the entry project worked as intended.  I also updated the code so it would make sure most fo the code was working.  Tommrow I will add the extra features.</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1083,24 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C26" s="4"/>
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="4">
+        <v>193</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46322</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C27" s="4"/>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76B81E0-1B5E-7043-8707-8ADB07BF2546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD70CD-B859-8D43-8050-A3C039046044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4660" yWindow="880" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
   </si>
   <si>
-    <t>9:00 PM - 12:12 PM</t>
-  </si>
-  <si>
-    <t>During this I finished the rest of the entries in the testing script.  This made sure the entry project worked as intended.  I also updated the code so it would make sure most fo the code was working.  Tommrow I will add the extra features.</t>
+    <t>9:00 PM - 12:45 PM</t>
+  </si>
+  <si>
+    <t>During this I finished the rest of the entries in the testing script.  This made sure the entry project worked as intended.  I also updated the code so it would make sure most fo the code was working.  I also added all the content to my notebook entry.  Tommrow I will add the extra features.</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1090,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="4">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="D26" s="2">
         <v>46322</v>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD70CD-B859-8D43-8050-A3C039046044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDBA31-AB64-A545-B581-557CDC35C780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4660" yWindow="880" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="4680" yWindow="1060" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -170,28 +170,28 @@
     <t>1:30PM</t>
   </si>
   <si>
-    <t>During this time period I have intergrated some of the function into the system we are programming.  This was done on Excel document.  I have included the function names.  I have also included some of their discription and the number of function as a demo of the page.</t>
-  </si>
-  <si>
-    <t>During this time period I added further documentation to the program function.  This allow for me to showcase how the program function work.  This would allow for me to document if the program is working as intended.</t>
-  </si>
-  <si>
     <t>During this time period in class we worked on the project and incoperated a bunch of the core resources for the program.  This made sure the project had been intergrated as intended.  It also make sure all the components in the project were working as intended.  This would allow for me to do the project like I was required to.  However, it also made sure the cores services in the project were integrated as intended.</t>
   </si>
   <si>
-    <t xml:space="preserve">During this time I added some of the testing script information back.  This made sure the program worked as intended.  The program would work properly if I did that. However, it did not appear to be full done which was the source of my worry.  </t>
-  </si>
-  <si>
     <t>3:40 PM - 5:00 PM</t>
   </si>
   <si>
-    <t xml:space="preserve">During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
-  </si>
-  <si>
     <t>9:00 PM - 12:45 PM</t>
   </si>
   <si>
-    <t>During this I finished the rest of the entries in the testing script.  This made sure the entry project worked as intended.  I also updated the code so it would make sure most fo the code was working.  I also added all the content to my notebook entry.  Tommrow I will add the extra features.</t>
+    <t>Lexa: During this time period I have intergrated some of the function into the system we are programming.  This was done on Excel document.  I have included the function names.  I have also included some of their discription and the number of function as a demo of the page.</t>
+  </si>
+  <si>
+    <t>Lexa: During this time period I added further documentation to the program function.  This allow for me to showcase how the program function work.  This would allow for me to document if the program is working as intended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lexa: During this time I added some of the testing script information back.  This made sure the program worked as intended.  The program would work properly if I did that. However, it did not appear to be full done which was the source of my worry.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lexa: During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
+  </si>
+  <si>
+    <t>Lexa: During this I finished the rest of the entries in the testing script.  This made sure the entry project worked as intended.  I also updated the code so it would make sure most fo the code was working.  I also added all the content to my notebook entry.  Tommrow I will add the extra features.</t>
   </si>
 </sst>
 </file>
@@ -999,7 +999,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1019,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1059,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1067,7 +1067,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4">
         <v>80</v>
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1087,7 +1087,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4">
         <v>225</v>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDBA31-AB64-A545-B581-557CDC35C780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1060" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
+    <workbookView xWindow="4680" yWindow="520" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Timetracker Sheet.xlsx
+++ b/Timetracker Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexahope/Documents/GitHub/Ophelias-Oasis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD4F264-2070-AA41-A36A-F793F358C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{6AD4F264-2070-AA41-A36A-F793F358C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41418EB-9AD7-4993-A842-F80939E958F5}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="19880" xr2:uid="{DC8A763E-506D-49AB-8E26-20F95A084029}"/>
   </bookViews>
@@ -39,11 +39,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
   <si>
     <t>Event:</t>
   </si>
   <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Hours worked</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date:  </t>
   </si>
   <si>
@@ -80,96 +86,90 @@
     <t>5:52PM</t>
   </si>
   <si>
+    <t>Cristian, created the project notebook which serves as the layout for the project.</t>
+  </si>
+  <si>
     <t>5:50PM</t>
   </si>
   <si>
+    <t>Cristian, created the requirements database for listing the functional and non-functional requirements of the project.</t>
+  </si>
+  <si>
     <t>6:30PM</t>
   </si>
   <si>
+    <t>6:15AM</t>
+  </si>
+  <si>
     <t>Lexa created the testing script records that keeps track of all transactions from testing.</t>
   </si>
   <si>
-    <t>6:15AM</t>
+    <t>8:55AM</t>
   </si>
   <si>
     <t>Lexa linked everyone for tracking bugs in the project. Lexa was able to make sure that eveyone was able to get into the github page so that everyone could connect to the server. Lexa was able to reach out the team mates when they were not able to contact the main server. Lexa was able to manage the feature and task on the project to make sure the project worked as intended.</t>
   </si>
   <si>
-    <t>8:55AM</t>
+    <t>7:42PM</t>
   </si>
   <si>
     <t>Lexa created the time tracker sheet to document all group activity in chronological order.</t>
   </si>
   <si>
-    <t>7:42PM</t>
+    <t>Evan created the draft document for the UML diagram that will utilized for the first turn-in checkpoint on the 24th. Edit: Changed websites to one more familiar to teammates</t>
+  </si>
+  <si>
+    <t>6:47PM</t>
   </si>
   <si>
     <t>Sean created a proposal text file going over Lexa's comments for testing.  Lexa preposed using an excel document to track the program requirements and then analysis the program using the requirement document.</t>
   </si>
   <si>
+    <t>8:36 AM - 11:56 AM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lexa, create a text file for tracking the project's data on project failures and functions.  Then integrate as much of that code as possible into the project.  This project is stored in Visual Studio.  </t>
   </si>
   <si>
-    <t>8:36 AM - 11:56 AM</t>
+    <t>8:30PM - 12:00AM</t>
   </si>
   <si>
     <t>Lexa, finalized the testing script plans and linked it to the Excel document.  Now the program test should be able to sync with the Excel document on macOS and test our program.  This will decrease the total development time.</t>
   </si>
   <si>
-    <t>Time</t>
+    <t>2:00 PM - 4:00PM</t>
   </si>
   <si>
     <t>Cristian, worked on project book.</t>
   </si>
   <si>
-    <t>Minutes Worked</t>
-  </si>
-  <si>
     <t>Cristian, worked on creating requirements.</t>
   </si>
   <si>
-    <t>Cristian, created the requirements database for listing the functional and non-functional requirements of the project.</t>
-  </si>
-  <si>
-    <t>Cristian, created the project notebook which serves as the layout for the project.</t>
+    <t>9:20AM - 10:35AM</t>
   </si>
   <si>
     <t>Sean made a rough estimate of the unadjusted FP computation based on the requirements database.</t>
   </si>
   <si>
+    <t>9:00AM - 12:20PM</t>
+  </si>
+  <si>
     <t>Evan created the UML use case diagram and completed part 6b on the Notebook Template (Discussion of requirements analysis)</t>
   </si>
   <si>
-    <t>Evan created the draft document for the UML diagram that will utilized for the first turn-in checkpoint on the 24th. Edit: Changed websites to one more familiar to teammates</t>
-  </si>
-  <si>
-    <t>9:20AM - 10:35AM</t>
+    <t>1:30PM</t>
   </si>
   <si>
     <t>Cristian, Worked on finishing up the project notebook</t>
   </si>
   <si>
-    <t>6:47PM</t>
+    <t>2:00PM</t>
   </si>
   <si>
     <t>Fabian finalized the Project Notebook and the Timetracker Sheet and submitted them for the project's 1st deliverable.</t>
   </si>
   <si>
-    <t>2:00 PM - 4:00PM</t>
-  </si>
-  <si>
-    <t>8:30PM - 12:00AM</t>
-  </si>
-  <si>
-    <t>9:00AM - 12:20PM</t>
-  </si>
-  <si>
-    <t>2:00PM</t>
-  </si>
-  <si>
-    <t>1:30PM</t>
-  </si>
-  <si>
     <t>During this time period I have intergrated some of the function into the system we are programming.  This was done on Excel document.  I have included the function names.  I have also included some of their discription and the number of function as a demo of the page.</t>
   </si>
   <si>
@@ -179,6 +179,12 @@
     <t>During this time period in class we worked on the project and incoperated a bunch of the core resources for the program.  This made sure the project had been intergrated as intended.  It also make sure all the components in the project were working as intended.  This would allow for me to do the project like I was required to.  However, it also made sure the cores services in the project were integrated as intended.</t>
   </si>
   <si>
+    <t>Edwin, started the website template</t>
+  </si>
+  <si>
+    <t>Edwin, finished website template</t>
+  </si>
+  <si>
     <t xml:space="preserve">During this time I added some of the testing script information back.  This made sure the program worked as intended.  The program would work properly if I did that. However, it did not appear to be full done which was the source of my worry.  </t>
   </si>
   <si>
@@ -186,13 +192,58 @@
   </si>
   <si>
     <t xml:space="preserve">During this time I added some entries into the testing script.  This made sure the testing script was up to date with all the required entries.  </t>
+  </si>
+  <si>
+    <t>11:00AM-2:00PM</t>
+  </si>
+  <si>
+    <t>Evan, created the Ophelias Oasis Logo</t>
+  </si>
+  <si>
+    <t>9:20PM-9:50PM</t>
+  </si>
+  <si>
+    <t>Sean, updated FP computation</t>
+  </si>
+  <si>
+    <t>9:50AM-11:31AM</t>
+  </si>
+  <si>
+    <t>Evan, updated Requirements part of 2nd Deliverable, worked on finishing the logo</t>
+  </si>
+  <si>
+    <t>Cristian created database tables, created react project, setup supabase client to react project</t>
+  </si>
+  <si>
+    <t>Cristian created ways to navigate to different pages. So far, only identifiers saying that it's the page is there. Created the structure for users to be able to sign up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristian added a way for users to log in to their accounts. Also added on both sign up and log in that once they successfully, they go to the reservations page. </t>
+  </si>
+  <si>
+    <t>10/21/1026</t>
+  </si>
+  <si>
+    <t>Cristian started the reservation form. Still needs to handle the submission and check whether the resrvation type conditions are met.</t>
+  </si>
+  <si>
+    <t>Cristian made it so that reservations can be made. All thats left for this is to confirm the condition for incentive reservations. It's missing the check on the average expected occupancy rate.</t>
+  </si>
+  <si>
+    <t>Cristian made is so that incentive reservations get the average expected occupancy by using bookings that already exist.</t>
+  </si>
+  <si>
+    <t>Cristian worked on project notebook. Created database dictionary/data modeling presentation.</t>
+  </si>
+  <si>
+    <t>Cristian worked on the project notebook. Created top level architecture diagram, detailed design, requirements mapping, notes on design, risk status section, updated sections 4b iv and 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,8 +277,8 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,521 +613,723 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DDD181-B1D7-4F70-9DC0-57E51E6395B2}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="175.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="175.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.5</v>
       </c>
       <c r="D2" s="2">
         <v>46266</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.75</v>
       </c>
       <c r="D3" s="2">
         <v>46268</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>11</v>
+      </c>
       <c r="D4" s="2">
         <v>46269</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75</v>
       </c>
       <c r="D5" s="2">
         <v>46277</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.25</v>
       </c>
       <c r="D6" s="2">
         <v>46280</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>18</v>
+      </c>
       <c r="D7" s="2">
         <v>46280</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4"/>
+        <v>19</v>
+      </c>
       <c r="D8" s="2">
         <v>46281</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4"/>
+        <v>21</v>
+      </c>
       <c r="D9" s="2">
         <v>46281</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.25</v>
       </c>
       <c r="D10" s="2">
         <v>46281</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4"/>
+        <v>16</v>
+      </c>
       <c r="D11" s="2">
         <v>46284</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>26</v>
+      </c>
       <c r="D12" s="2">
         <v>46287</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>28</v>
+      </c>
       <c r="D13" s="2">
         <v>46285</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="4">
-        <v>210</v>
+        <v>30</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3.5</v>
       </c>
       <c r="D14" s="2">
         <v>46289</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4">
-        <v>120</v>
+        <v>32</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
       </c>
       <c r="D15" s="2">
         <v>46281</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="C16" s="4">
-        <v>44</v>
+      <c r="C16" s="5">
+        <v>0.75</v>
       </c>
       <c r="D16" s="2">
         <v>46289</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="4">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.25</v>
       </c>
       <c r="D17" s="2">
         <v>46289</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="4">
-        <v>200</v>
+        <v>37</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3.25</v>
       </c>
       <c r="D18" s="2">
         <v>46289</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="4">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.5</v>
       </c>
       <c r="D19" s="2">
         <v>46289</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="4">
-        <v>15</v>
+      <c r="C20" s="5">
+        <v>0.25</v>
       </c>
       <c r="D20" s="2">
         <v>46289</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="3">
         <v>0.89583333333333337</v>
       </c>
-      <c r="C21" s="4">
-        <v>60</v>
+      <c r="C21" s="5">
+        <v>1</v>
       </c>
       <c r="D21" s="2">
         <v>46288</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="3">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C22" s="4">
-        <v>60</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
         <v>46318</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="3">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C23" s="4">
-        <v>45</v>
+      <c r="C23" s="5">
+        <v>0.75</v>
       </c>
       <c r="D23" s="2">
         <v>46287</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="4">
-        <v>120</v>
+      <c r="B24" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1.5</v>
       </c>
       <c r="D24" s="2">
-        <v>46320</v>
+        <v>46314</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="4">
-        <v>80</v>
-      </c>
-      <c r="D25" s="2">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46320</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="D27" s="2">
         <v>46322</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C34" s="4"/>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="5">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46323</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46323</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46324</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="D33" s="2">
+        <v>46311</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2">
+        <v>46317</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>46318</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>46322</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="C38" s="5">
+        <v>6</v>
+      </c>
+      <c r="D38" s="2">
+        <v>46323</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
